--- a/data/trans_orig/P05A06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2012 (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>576653</t>
+          <t>576971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>612901</t>
+          <t>616873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>554047</t>
+          <t>555029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>594623</t>
+          <t>596693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1145462</t>
+          <t>1143959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1198519</t>
+          <t>1196639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76883</t>
+          <t>73913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112261</t>
+          <t>110227</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91139</t>
+          <t>89000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130038</t>
+          <t>128479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176886</t>
+          <t>176922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228182</t>
+          <t>227076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19108</t>
+          <t>21032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32169</t>
+          <t>32750</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>704712</t>
+          <t>702808</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>762801</t>
+          <t>762466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>724434</t>
+          <t>722231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>781232</t>
+          <t>783249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1445152</t>
+          <t>1446834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1530080</t>
+          <t>1529243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>213647</t>
+          <t>215951</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>269433</t>
+          <t>272025</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221140</t>
+          <t>221698</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>277283</t>
+          <t>279029</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>450528</t>
+          <t>455144</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>533989</t>
+          <t>530809</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22810</t>
+          <t>20922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48789</t>
+          <t>46259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38759</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75930</t>
+          <t>76996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497062</t>
+          <t>498681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>552659</t>
+          <t>552047</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>513351</t>
+          <t>513451</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>567450</t>
+          <t>564787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1026997</t>
+          <t>1028511</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1099380</t>
+          <t>1099148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183183</t>
+          <t>183455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>235104</t>
+          <t>234454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180560</t>
+          <t>182075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232329</t>
+          <t>232939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379304</t>
+          <t>378578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446541</t>
+          <t>448617</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14784</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34077</t>
+          <t>34097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39460</t>
+          <t>39172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36785</t>
+          <t>37474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66207</t>
+          <t>66667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>539170</t>
+          <t>539423</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>602166</t>
+          <t>599743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>608953</t>
+          <t>605756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>673060</t>
+          <t>673418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1169988</t>
+          <t>1166059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1257874</t>
+          <t>1254326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>272998</t>
+          <t>278556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333665</t>
+          <t>335834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>319382</t>
+          <t>314382</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380320</t>
+          <t>380693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>605845</t>
+          <t>609145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>689024</t>
+          <t>694056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50382</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83731</t>
+          <t>85002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>41687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70738</t>
+          <t>71496</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101344</t>
+          <t>100228</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141218</t>
+          <t>145561</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2370677</t>
+          <t>2373160</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2484371</t>
+          <t>2480058</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2448334</t>
+          <t>2451318</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2564878</t>
+          <t>2558730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4860721</t>
+          <t>4862065</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5018440</t>
+          <t>5015343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>794985</t>
+          <t>796370</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>901057</t>
+          <t>895318</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>855530</t>
+          <t>863626</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>961751</t>
+          <t>967037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1680810</t>
+          <t>1683984</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1827751</t>
+          <t>1830193</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111618</t>
+          <t>113910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>158155</t>
+          <t>159441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99266</t>
+          <t>97803</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143646</t>
+          <t>141059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>225439</t>
+          <t>221422</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>285568</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>587575</t>
+          <t>588503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>617525</t>
+          <t>618660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>576971</t>
+          <t>577142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>608518</t>
+          <t>608207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1177355</t>
+          <t>1176567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1222265</t>
+          <t>1222364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45395</t>
+          <t>43256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74151</t>
+          <t>73897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51627</t>
+          <t>52122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81250</t>
+          <t>82047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101939</t>
+          <t>101674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144275</t>
+          <t>145367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>24191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>819980</t>
+          <t>825123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>873789</t>
+          <t>872332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>835190</t>
+          <t>833980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>884779</t>
+          <t>886212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1674190</t>
+          <t>1673257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1747284</t>
+          <t>1743334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130738</t>
+          <t>132344</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>182213</t>
+          <t>178189</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135426</t>
+          <t>134686</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181841</t>
+          <t>183776</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>276582</t>
+          <t>278983</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>348239</t>
+          <t>348777</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>24289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>25498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21661</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43883</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>493661</t>
+          <t>495386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>548488</t>
+          <t>548879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>518225</t>
+          <t>514877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>570657</t>
+          <t>568119</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1030558</t>
+          <t>1027597</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1102526</t>
+          <t>1101682</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177316</t>
+          <t>176304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228987</t>
+          <t>228642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183905</t>
+          <t>189224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>234934</t>
+          <t>238530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377476</t>
+          <t>378528</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448238</t>
+          <t>446394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>46193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15487</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>36823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44576</t>
+          <t>44008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75454</t>
+          <t>76599</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>569773</t>
+          <t>570915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>627405</t>
+          <t>629193</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>645686</t>
+          <t>644241</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>709942</t>
+          <t>708738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1234135</t>
+          <t>1231021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1319543</t>
+          <t>1315969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>244862</t>
+          <t>244389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>297526</t>
+          <t>301195</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>257145</t>
+          <t>255785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>316101</t>
+          <t>315169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>516526</t>
+          <t>517873</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>595603</t>
+          <t>600380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49581</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80514</t>
+          <t>81396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>53252</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88216</t>
+          <t>86815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>110863</t>
+          <t>111472</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158071</t>
+          <t>159591</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2526537</t>
+          <t>2530597</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2624790</t>
+          <t>2631855</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2616736</t>
+          <t>2625532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2725308</t>
+          <t>2731399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5180940</t>
+          <t>5180660</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5324212</t>
+          <t>5323665</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>636959</t>
+          <t>634101</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>731125</t>
+          <t>727126</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>671500</t>
+          <t>667810</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>772633</t>
+          <t>768259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1333673</t>
+          <t>1329451</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1465255</t>
+          <t>1472085</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97728</t>
+          <t>98658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>142097</t>
+          <t>141005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97066</t>
+          <t>98995</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141938</t>
+          <t>141886</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>206895</t>
+          <t>207919</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>269308</t>
+          <t>270301</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023</t>
+          <t>Población según si en el barrio donde vive hay delincuencia/inseguridad en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>595857</t>
+          <t>595904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>617309</t>
+          <t>617272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>681414</t>
+          <t>679055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>703156</t>
+          <t>702784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1284307</t>
+          <t>1285382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1315888</t>
+          <t>1314095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34971</t>
+          <t>36440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35646</t>
+          <t>37441</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65699</t>
+          <t>63746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>19226</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1052272</t>
+          <t>1044785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1137174</t>
+          <t>1140879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>830414</t>
+          <t>827698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>865741</t>
+          <t>864364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1893738</t>
+          <t>1895530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2003622</t>
+          <t>2005130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33820</t>
+          <t>35148</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100283</t>
+          <t>101071</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67640</t>
+          <t>67529</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96611</t>
+          <t>98401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>102315</t>
+          <t>102272</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>183357</t>
+          <t>186717</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53529</t>
+          <t>54557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>17956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>40183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37766</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80553</t>
+          <t>83064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>502888</t>
+          <t>504599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>557347</t>
+          <t>558831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>710986</t>
+          <t>710729</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>842927</t>
+          <t>843273</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1239177</t>
+          <t>1234880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1409486</t>
+          <t>1419116</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106888</t>
+          <t>107142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152476</t>
+          <t>153399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71727</t>
+          <t>70329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180080</t>
+          <t>181774</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172354</t>
+          <t>169307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>312947</t>
+          <t>317883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61006</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42374</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92388</t>
+          <t>92286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>649138</t>
+          <t>651048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>707179</t>
+          <t>708230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>755167</t>
+          <t>754503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>848100</t>
+          <t>847116</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1417064</t>
+          <t>1418982</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1528045</t>
+          <t>1529319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177606</t>
+          <t>177607</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152943</t>
+          <t>151530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204239</t>
+          <t>204707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175690</t>
+          <t>173145</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>247116</t>
+          <t>248348</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>348480</t>
+          <t>349868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>435399</t>
+          <t>437746</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52252</t>
+          <t>53395</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88330</t>
+          <t>87087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,49 +7365,49 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>84624</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>66620</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>104338</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>9,56%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>84624</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>65431</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>103231</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>198</t>
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128098</t>
+          <t>129037</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>180615</t>
+          <t>179087</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2841358</t>
+          <t>2847254</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3029487</t>
+          <t>3023150</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3030929</t>
+          <t>3030764</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3196334</t>
+          <t>3201188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5901152</t>
+          <t>5907290</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6136752</t>
+          <t>6173974</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>309567</t>
+          <t>310272</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>447893</t>
+          <t>448554</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>383699</t>
+          <t>379159</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>514116</t>
+          <t>511904</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>761411</t>
+          <t>740484</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>946380</t>
+          <t>941858</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109900</t>
+          <t>111463</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181725</t>
+          <t>179065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117127</t>
+          <t>117452</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>171050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>249303</t>
+          <t>239972</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>334324</t>
+          <t>330670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A06-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>576971</t>
+          <t>574579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>616873</t>
+          <t>614639</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>555029</t>
+          <t>554923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>596693</t>
+          <t>594779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1143959</t>
+          <t>1146305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1196639</t>
+          <t>1202177</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73913</t>
+          <t>74985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110227</t>
+          <t>113841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89000</t>
+          <t>91183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128479</t>
+          <t>130973</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176922</t>
+          <t>174098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227076</t>
+          <t>226168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17378</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>31211</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>702808</t>
+          <t>705346</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>762466</t>
+          <t>762979</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>722231</t>
+          <t>721057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>783249</t>
+          <t>780835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1446834</t>
+          <t>1443108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1529243</t>
+          <t>1532424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>215951</t>
+          <t>216722</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>272025</t>
+          <t>272284</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221698</t>
+          <t>222208</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>279029</t>
+          <t>279347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>455144</t>
+          <t>447969</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>530809</t>
+          <t>534347</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46259</t>
+          <t>47131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38756</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76996</t>
+          <t>75640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>498681</t>
+          <t>498741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>552047</t>
+          <t>551236</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>513451</t>
+          <t>514280</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>564787</t>
+          <t>566116</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1028511</t>
+          <t>1028919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1099148</t>
+          <t>1101602</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183455</t>
+          <t>182215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234454</t>
+          <t>234122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182075</t>
+          <t>179235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232939</t>
+          <t>231418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378578</t>
+          <t>376639</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448617</t>
+          <t>450387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34097</t>
+          <t>33951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39172</t>
+          <t>40378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>37128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66667</t>
+          <t>66891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>539423</t>
+          <t>538449</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>599743</t>
+          <t>599492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>605756</t>
+          <t>609797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>673418</t>
+          <t>674792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1166059</t>
+          <t>1167699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1254326</t>
+          <t>1256251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>278556</t>
+          <t>276562</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335834</t>
+          <t>334711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314382</t>
+          <t>314158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380693</t>
+          <t>377394</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>609145</t>
+          <t>610101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>694056</t>
+          <t>693969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>50294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85002</t>
+          <t>84210</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41687</t>
+          <t>41621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71496</t>
+          <t>70713</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100228</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>145561</t>
+          <t>145452</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2373160</t>
+          <t>2370101</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2480058</t>
+          <t>2476910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2451318</t>
+          <t>2446841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2558730</t>
+          <t>2562951</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4862065</t>
+          <t>4861156</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5015343</t>
+          <t>5014272</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>796370</t>
+          <t>800218</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>895318</t>
+          <t>903311</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>863626</t>
+          <t>858300</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>967037</t>
+          <t>967731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1683984</t>
+          <t>1685004</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1830193</t>
+          <t>1831957</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113910</t>
+          <t>110594</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159441</t>
+          <t>159516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97803</t>
+          <t>96256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141059</t>
+          <t>139641</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>221422</t>
+          <t>219098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>285568</t>
+          <t>286805</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>588503</t>
+          <t>586782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>618660</t>
+          <t>619074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>577142</t>
+          <t>578286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>610112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1176567</t>
+          <t>1176287</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1222364</t>
+          <t>1221429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43256</t>
+          <t>43516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73897</t>
+          <t>74472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52122</t>
+          <t>50160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82047</t>
+          <t>80774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101674</t>
+          <t>101556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145367</t>
+          <t>144895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24191</t>
+          <t>24892</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>825123</t>
+          <t>819359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>872332</t>
+          <t>869480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>833980</t>
+          <t>837051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>886212</t>
+          <t>885187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1673257</t>
+          <t>1672394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1743334</t>
+          <t>1746210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132344</t>
+          <t>135047</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>178189</t>
+          <t>182075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>134686</t>
+          <t>134439</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>183776</t>
+          <t>180485</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>278983</t>
+          <t>277206</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>348777</t>
+          <t>346019</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24289</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>21085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>42744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>495386</t>
+          <t>499552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>548879</t>
+          <t>550141</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>514877</t>
+          <t>517349</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>568119</t>
+          <t>568815</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1027597</t>
+          <t>1031809</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1101682</t>
+          <t>1108103</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,14%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176304</t>
+          <t>175468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228642</t>
+          <t>224034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189224</t>
+          <t>186228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238530</t>
+          <t>234585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378528</t>
+          <t>375986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446394</t>
+          <t>446745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22735</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46193</t>
+          <t>46177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36823</t>
+          <t>37277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44008</t>
+          <t>43114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76599</t>
+          <t>74147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>570915</t>
+          <t>568512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>629193</t>
+          <t>628022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>644241</t>
+          <t>644075</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>708738</t>
+          <t>705196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1231021</t>
+          <t>1233502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1315969</t>
+          <t>1323286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>244389</t>
+          <t>243903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>301195</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255785</t>
+          <t>257006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>315169</t>
+          <t>315803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>517873</t>
+          <t>512225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>600380</t>
+          <t>597604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50578</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81396</t>
+          <t>79279</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,49 +4853,49 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>69901</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>56040</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>89985</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>8,72%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>69901</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>53252</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>86815</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>124</t>
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>111472</t>
+          <t>111076</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>159591</t>
+          <t>155719</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2530597</t>
+          <t>2524371</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2631855</t>
+          <t>2622349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2625532</t>
+          <t>2624186</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2731399</t>
+          <t>2726526</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5180660</t>
+          <t>5177574</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5323665</t>
+          <t>5315483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>634101</t>
+          <t>636677</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>727126</t>
+          <t>729294</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>667810</t>
+          <t>669863</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>768259</t>
+          <t>766943</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1329451</t>
+          <t>1340613</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1472085</t>
+          <t>1476494</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98658</t>
+          <t>98144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141005</t>
+          <t>139187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98995</t>
+          <t>100001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141886</t>
+          <t>143598</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>207527</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>270301</t>
+          <t>269485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -5751,32 +5751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>608735</t>
+          <t>662921</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>595904</t>
+          <t>650124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>617272</t>
+          <t>672190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5786,32 +5786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>693545</t>
+          <t>699765</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>679055</t>
+          <t>687517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>702784</t>
+          <t>708369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1302281</t>
+          <t>1362685</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1285382</t>
+          <t>1345890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1314095</t>
+          <t>1376914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -5864,32 +5864,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36440</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5899,32 +5899,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>27935</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37441</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>49283</t>
+          <t>52357</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>39474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63746</t>
+          <t>67299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6047,32 +6047,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19226</t>
+          <t>20891</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6090,17 +6090,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634021</t>
+          <t>689200</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634021</t>
+          <t>689200</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634021</t>
+          <t>689200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1359352</t>
+          <t>1423380</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1359352</t>
+          <t>1423380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1359352</t>
+          <t>1423380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6207,32 +6207,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1088664</t>
+          <t>939552</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1044785</t>
+          <t>911879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1140879</t>
+          <t>958815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6242,32 +6242,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>848688</t>
+          <t>950264</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>827698</t>
+          <t>931096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>864364</t>
+          <t>968096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6277,32 +6277,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1937353</t>
+          <t>1889816</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1895530</t>
+          <t>1859521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2005130</t>
+          <t>1918523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6320,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66989</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35148</t>
+          <t>52419</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101071</t>
+          <t>89250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6355,32 +6355,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81479</t>
+          <t>90217</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67529</t>
+          <t>74968</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98401</t>
+          <t>106137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>148467</t>
+          <t>158815</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>102272</t>
+          <t>136406</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>186717</t>
+          <t>188514</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -6433,32 +6433,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36431</t>
+          <t>39764</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>56790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6468,32 +6468,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>42433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>62226</t>
+          <t>67374</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40099</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83064</t>
+          <t>85756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -6546,17 +6546,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192084</t>
+          <t>1047914</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192084</t>
+          <t>1047914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192084</t>
+          <t>1047914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>955962</t>
+          <t>1068092</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>955962</t>
+          <t>1068092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>955962</t>
+          <t>1068092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2148046</t>
+          <t>2116006</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2148046</t>
+          <t>2116006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2148046</t>
+          <t>2116006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6663,32 +6663,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>532660</t>
+          <t>604724</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>504599</t>
+          <t>575265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>558831</t>
+          <t>633178</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6698,32 +6698,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>767008</t>
+          <t>620369</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>710729</t>
+          <t>595392</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>843273</t>
+          <t>642585</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1299668</t>
+          <t>1225092</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1234880</t>
+          <t>1187436</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1419116</t>
+          <t>1261306</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -6776,32 +6776,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>128385</t>
+          <t>152324</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107142</t>
+          <t>129271</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153399</t>
+          <t>178845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6811,32 +6811,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>134014</t>
+          <t>152792</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70329</t>
+          <t>131606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181774</t>
+          <t>175907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>262399</t>
+          <t>305115</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169307</t>
+          <t>273155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>317883</t>
+          <t>340947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -6889,32 +6889,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>39611</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24281</t>
+          <t>26754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>60414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6924,32 +6924,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29096</t>
+          <t>35107</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>26052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>67661</t>
+          <t>74718</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43346</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92286</t>
+          <t>96878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -7002,17 +7002,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>699610</t>
+          <t>796659</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>699610</t>
+          <t>796659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>699610</t>
+          <t>796659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7037,17 +7037,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>930118</t>
+          <t>808267</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>930118</t>
+          <t>808267</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>930118</t>
+          <t>808267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1629728</t>
+          <t>1604925</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1629728</t>
+          <t>1604925</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1629728</t>
+          <t>1604925</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>678096</t>
+          <t>719156</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>651048</t>
+          <t>687596</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>708230</t>
+          <t>748064</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>786447</t>
+          <t>766094</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>754503</t>
+          <t>739719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>847116</t>
+          <t>792091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1464543</t>
+          <t>1485250</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1418982</t>
+          <t>1443366</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1529319</t>
+          <t>1527759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177607</t>
+          <t>189824</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151530</t>
+          <t>165300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204707</t>
+          <t>220725</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7267,32 +7267,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>220162</t>
+          <t>246376</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173145</t>
+          <t>222645</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248348</t>
+          <t>269858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>397769</t>
+          <t>436200</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349868</t>
+          <t>401236</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437746</t>
+          <t>474652</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -7345,32 +7345,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68024</t>
+          <t>77200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53395</t>
+          <t>61631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87087</t>
+          <t>100051</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>84624</t>
+          <t>101999</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66620</t>
+          <t>85410</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104338</t>
+          <t>122189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>179199</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>129037</t>
+          <t>155312</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>179087</t>
+          <t>206671</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -7458,17 +7458,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>923726</t>
+          <t>986180</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>923726</t>
+          <t>986180</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>923726</t>
+          <t>986180</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7493,17 +7493,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1091233</t>
+          <t>1114469</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1091233</t>
+          <t>1114469</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1091233</t>
+          <t>1114469</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2014960</t>
+          <t>2100649</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2014960</t>
+          <t>2100649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2014960</t>
+          <t>2100649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2908157</t>
+          <t>2926353</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2847254</t>
+          <t>2870584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3023150</t>
+          <t>2974759</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3095688</t>
+          <t>3036490</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3030764</t>
+          <t>2985912</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3201188</t>
+          <t>3078779</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6003845</t>
+          <t>5962844</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5907290</t>
+          <t>5897423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6173974</t>
+          <t>6029137</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>396272</t>
+          <t>435167</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310272</t>
+          <t>394162</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>482171</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7723,32 +7723,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>461647</t>
+          <t>517320</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>379159</t>
+          <t>480748</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>511904</t>
+          <t>564479</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>857919</t>
+          <t>952487</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>740484</t>
+          <t>892278</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>941858</t>
+          <t>1012514</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -7801,32 +7801,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>145015</t>
+          <t>158433</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111463</t>
+          <t>133446</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179065</t>
+          <t>193593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7836,32 +7836,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>145308</t>
+          <t>171197</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117452</t>
+          <t>146893</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171050</t>
+          <t>198268</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>290323</t>
+          <t>329630</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>239972</t>
+          <t>293762</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>330670</t>
+          <t>370437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -7914,17 +7914,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3449443</t>
+          <t>3519953</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3449443</t>
+          <t>3519953</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3449443</t>
+          <t>3519953</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7949,17 +7949,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3702643</t>
+          <t>3725007</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3702643</t>
+          <t>3725007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3702643</t>
+          <t>3725007</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7152086</t>
+          <t>7244961</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7152086</t>
+          <t>7244961</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7152086</t>
+          <t>7244961</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
